--- a/data/uploads/zhuanhua_demo.xlsx
+++ b/data/uploads/zhuanhua_demo.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="11740"/>
+    <workbookView windowWidth="28000" windowHeight="11740"/>
   </bookViews>
   <sheets>
     <sheet name="sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet!$A$1:$V$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet!$A$1:$V$192</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="738">
   <si>
     <t>日期</t>
   </si>
@@ -2034,6 +2034,216 @@
   </si>
   <si>
     <t>0.02388872</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>747</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>2.61</t>
+  </si>
+  <si>
+    <t>0.00125064</t>
+  </si>
+  <si>
+    <t>0.01264637</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>6.73</t>
+  </si>
+  <si>
+    <t>0.00748782</t>
+  </si>
+  <si>
+    <t>0.02383459</t>
+  </si>
+  <si>
+    <t>0.00188206</t>
+  </si>
+  <si>
+    <t>0.03238095</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>514</t>
+  </si>
+  <si>
+    <t>3.92</t>
+  </si>
+  <si>
+    <t>0.00484357</t>
+  </si>
+  <si>
+    <t>0.01553433</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>0.00078494</t>
+  </si>
+  <si>
+    <t>0.00914797</t>
+  </si>
+  <si>
+    <t>836</t>
+  </si>
+  <si>
+    <t>11.00</t>
+  </si>
+  <si>
+    <t>0.01481481</t>
+  </si>
+  <si>
+    <t>0.03868579</t>
+  </si>
+  <si>
+    <t>6.80</t>
+  </si>
+  <si>
+    <t>0.00182837</t>
+  </si>
+  <si>
+    <t>0.02904990</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>3.69</t>
+  </si>
+  <si>
+    <t>0.00322896</t>
+  </si>
+  <si>
+    <t>0.01404768</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>681</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>8.41</t>
+  </si>
+  <si>
+    <t>0.00866016</t>
+  </si>
+  <si>
+    <t>0.03135503</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>1.72</t>
+  </si>
+  <si>
+    <t>0.00080930</t>
+  </si>
+  <si>
+    <t>0.00793651</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>6.28</t>
+  </si>
+  <si>
+    <t>0.00145740</t>
+  </si>
+  <si>
+    <t>0.02501593</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>510</t>
+  </si>
+  <si>
+    <t>3.81</t>
+  </si>
+  <si>
+    <t>0.00393525</t>
+  </si>
+  <si>
+    <t>0.01456228</t>
+  </si>
+  <si>
+    <t>1596</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>0.00104316</t>
+  </si>
+  <si>
+    <t>0.01185835</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>8.70</t>
+  </si>
+  <si>
+    <t>0.00711307</t>
+  </si>
+  <si>
+    <t>0.03060148</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>4.95</t>
+  </si>
+  <si>
+    <t>0.00129421</t>
+  </si>
+  <si>
+    <t>0.02179564</t>
+  </si>
+  <si>
+    <t>1174</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>9.78</t>
+  </si>
+  <si>
+    <t>0.00938262</t>
+  </si>
+  <si>
+    <t>0.03803291</t>
   </si>
 </sst>
 </file>
@@ -3047,8 +3257,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:V182"/>
+  <sheetPr/>
+  <dimension ref="A1:V203"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="7" width="16.8173076923077" customWidth="1"/>
@@ -3077,7 +3287,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:7">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -3100,7 +3310,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:7">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -3117,7 +3327,7 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" hidden="1" spans="1:7">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -3140,7 +3350,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:7">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -3163,7 +3373,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" hidden="1" spans="1:7">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -3186,7 +3396,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:7">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>35</v>
       </c>
@@ -3209,7 +3419,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:7">
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
@@ -3226,7 +3436,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" hidden="1" spans="1:7">
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
@@ -3249,7 +3459,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:7">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
@@ -3272,7 +3482,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:7">
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
@@ -3295,7 +3505,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:7">
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>56</v>
       </c>
@@ -3318,7 +3528,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:7">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>56</v>
       </c>
@@ -3335,7 +3545,7 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" hidden="1" spans="1:7">
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
         <v>56</v>
       </c>
@@ -3358,7 +3568,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:7">
+    <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
         <v>56</v>
       </c>
@@ -3381,7 +3591,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:7">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>56</v>
       </c>
@@ -3404,7 +3614,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:7">
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
         <v>76</v>
       </c>
@@ -3427,7 +3637,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:7">
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
         <v>76</v>
       </c>
@@ -3444,7 +3654,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" hidden="1" spans="1:7">
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
         <v>76</v>
       </c>
@@ -3467,7 +3677,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:7">
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
         <v>76</v>
       </c>
@@ -3490,7 +3700,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:7">
+    <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
         <v>76</v>
       </c>
@@ -3513,7 +3723,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="1:7">
+    <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
         <v>96</v>
       </c>
@@ -3536,7 +3746,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:7">
+    <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
         <v>96</v>
       </c>
@@ -3553,7 +3763,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" hidden="1" spans="1:7">
+    <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
         <v>96</v>
       </c>
@@ -3576,7 +3786,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:7">
+    <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
         <v>96</v>
       </c>
@@ -3599,7 +3809,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" hidden="1" spans="1:7">
+    <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
         <v>96</v>
       </c>
@@ -3622,7 +3832,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:7">
+    <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
         <v>116</v>
       </c>
@@ -3643,7 +3853,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:7">
+    <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
         <v>116</v>
       </c>
@@ -3660,7 +3870,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" hidden="1" spans="1:7">
+    <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
         <v>121</v>
       </c>
@@ -3683,7 +3893,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:7">
+    <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
         <v>121</v>
       </c>
@@ -3706,7 +3916,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:7">
+    <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
         <v>121</v>
       </c>
@@ -3729,7 +3939,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:7">
+    <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
         <v>121</v>
       </c>
@@ -3752,7 +3962,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:22">
+    <row r="33" spans="1:22">
       <c r="A33" s="1" t="s">
         <v>141</v>
       </c>
@@ -3775,7 +3985,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:22">
+    <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
         <v>141</v>
       </c>
@@ -3798,7 +4008,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:22">
+    <row r="35" spans="1:22">
       <c r="A35" s="1" t="s">
         <v>141</v>
       </c>
@@ -3824,7 +4034,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="36" hidden="1" spans="1:22">
+    <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
         <v>141</v>
       </c>
@@ -3847,7 +4057,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:22">
+    <row r="37" spans="1:22">
       <c r="A37" s="1" t="s">
         <v>159</v>
       </c>
@@ -3870,7 +4080,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:22">
+    <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
         <v>159</v>
       </c>
@@ -3887,7 +4097,7 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" hidden="1" spans="1:22">
+    <row r="39" spans="1:22">
       <c r="A39" s="1" t="s">
         <v>159</v>
       </c>
@@ -3910,7 +4120,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="40" hidden="1" spans="1:22">
+    <row r="40" spans="1:22">
       <c r="A40" s="1" t="s">
         <v>159</v>
       </c>
@@ -3933,7 +4143,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:22">
+    <row r="41" spans="1:22">
       <c r="A41" s="1" t="s">
         <v>159</v>
       </c>
@@ -3956,7 +4166,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="42" hidden="1" spans="1:22">
+    <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
         <v>177</v>
       </c>
@@ -3979,7 +4189,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:22">
+    <row r="43" spans="1:22">
       <c r="A43" s="1" t="s">
         <v>177</v>
       </c>
@@ -3996,7 +4206,7 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" hidden="1" spans="1:22">
+    <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
         <v>177</v>
       </c>
@@ -4019,7 +4229,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:22">
+    <row r="45" spans="1:22">
       <c r="A45" s="1" t="s">
         <v>177</v>
       </c>
@@ -4042,7 +4252,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:22">
+    <row r="46" spans="1:22">
       <c r="A46" s="1" t="s">
         <v>177</v>
       </c>
@@ -4065,7 +4275,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:22">
+    <row r="47" spans="1:22">
       <c r="A47" s="1" t="s">
         <v>198</v>
       </c>
@@ -4088,7 +4298,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:22">
+    <row r="48" spans="1:22">
       <c r="A48" s="1" t="s">
         <v>198</v>
       </c>
@@ -4105,7 +4315,7 @@
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" hidden="1" spans="1:7">
+    <row r="49" spans="1:7">
       <c r="A49" s="1" t="s">
         <v>198</v>
       </c>
@@ -4128,7 +4338,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:7">
+    <row r="50" spans="1:7">
       <c r="A50" s="1" t="s">
         <v>198</v>
       </c>
@@ -4151,7 +4361,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:7">
+    <row r="51" spans="1:7">
       <c r="A51" s="1" t="s">
         <v>198</v>
       </c>
@@ -4174,7 +4384,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:7">
+    <row r="52" spans="1:7">
       <c r="A52" s="1" t="s">
         <v>215</v>
       </c>
@@ -4197,7 +4407,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:7">
+    <row r="53" spans="1:7">
       <c r="A53" s="1" t="s">
         <v>215</v>
       </c>
@@ -4214,7 +4424,7 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" hidden="1" spans="1:7">
+    <row r="54" spans="1:7">
       <c r="A54" s="1" t="s">
         <v>215</v>
       </c>
@@ -4237,7 +4447,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:7">
+    <row r="55" spans="1:7">
       <c r="A55" s="1" t="s">
         <v>215</v>
       </c>
@@ -4260,7 +4470,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:7">
+    <row r="56" spans="1:7">
       <c r="A56" s="1" t="s">
         <v>215</v>
       </c>
@@ -4283,7 +4493,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:7">
+    <row r="57" spans="1:7">
       <c r="A57" s="1" t="s">
         <v>232</v>
       </c>
@@ -4300,7 +4510,7 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58" hidden="1" spans="1:7">
+    <row r="58" spans="1:7">
       <c r="A58" s="1" t="s">
         <v>232</v>
       </c>
@@ -4323,7 +4533,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:7">
+    <row r="59" spans="1:7">
       <c r="A59" s="1" t="s">
         <v>238</v>
       </c>
@@ -4346,7 +4556,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:7">
+    <row r="60" spans="1:7">
       <c r="A60" s="1" t="s">
         <v>238</v>
       </c>
@@ -4363,7 +4573,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" hidden="1" spans="1:7">
+    <row r="61" spans="1:7">
       <c r="A61" s="1" t="s">
         <v>238</v>
       </c>
@@ -4386,7 +4596,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:7">
+    <row r="62" spans="1:7">
       <c r="A62" s="1" t="s">
         <v>238</v>
       </c>
@@ -4409,7 +4619,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:7">
+    <row r="63" spans="1:7">
       <c r="A63" s="1" t="s">
         <v>238</v>
       </c>
@@ -4432,7 +4642,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:7">
+    <row r="64" spans="1:7">
       <c r="A64" s="1" t="s">
         <v>257</v>
       </c>
@@ -4455,7 +4665,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:7">
+    <row r="65" spans="1:7">
       <c r="A65" s="1" t="s">
         <v>257</v>
       </c>
@@ -4478,7 +4688,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:7">
+    <row r="66" spans="1:7">
       <c r="A66" s="1" t="s">
         <v>257</v>
       </c>
@@ -4501,7 +4711,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:7">
+    <row r="67" spans="1:7">
       <c r="A67" s="1" t="s">
         <v>257</v>
       </c>
@@ -4524,7 +4734,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:7">
+    <row r="68" spans="1:7">
       <c r="A68" s="1" t="s">
         <v>275</v>
       </c>
@@ -4547,7 +4757,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:7">
+    <row r="69" spans="1:7">
       <c r="A69" s="1" t="s">
         <v>275</v>
       </c>
@@ -4564,7 +4774,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" hidden="1" spans="1:7">
+    <row r="70" spans="1:7">
       <c r="A70" s="1" t="s">
         <v>275</v>
       </c>
@@ -4587,7 +4797,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:7">
+    <row r="71" spans="1:7">
       <c r="A71" s="1" t="s">
         <v>275</v>
       </c>
@@ -4610,7 +4820,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:7">
+    <row r="72" spans="1:7">
       <c r="A72" s="1" t="s">
         <v>275</v>
       </c>
@@ -4633,7 +4843,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:7">
+    <row r="73" spans="1:7">
       <c r="A73" s="1" t="s">
         <v>290</v>
       </c>
@@ -4656,7 +4866,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:7">
+    <row r="74" spans="1:7">
       <c r="A74" s="1" t="s">
         <v>290</v>
       </c>
@@ -4673,7 +4883,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" hidden="1" spans="1:7">
+    <row r="75" spans="1:7">
       <c r="A75" s="1" t="s">
         <v>290</v>
       </c>
@@ -4696,7 +4906,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:7">
+    <row r="76" spans="1:7">
       <c r="A76" s="1" t="s">
         <v>290</v>
       </c>
@@ -4719,7 +4929,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:7">
+    <row r="77" spans="1:7">
       <c r="A77" s="1" t="s">
         <v>290</v>
       </c>
@@ -4742,7 +4952,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:7">
+    <row r="78" spans="1:7">
       <c r="A78" s="1" t="s">
         <v>306</v>
       </c>
@@ -4765,7 +4975,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:7">
+    <row r="79" spans="1:7">
       <c r="A79" s="1" t="s">
         <v>306</v>
       </c>
@@ -4782,7 +4992,7 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" hidden="1" spans="1:7">
+    <row r="80" spans="1:7">
       <c r="A80" s="1" t="s">
         <v>306</v>
       </c>
@@ -4805,7 +5015,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:7">
+    <row r="81" spans="1:7">
       <c r="A81" s="1" t="s">
         <v>306</v>
       </c>
@@ -4828,7 +5038,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:7">
+    <row r="82" spans="1:7">
       <c r="A82" s="1" t="s">
         <v>306</v>
       </c>
@@ -4851,7 +5061,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:7">
+    <row r="83" spans="1:7">
       <c r="A83" s="1" t="s">
         <v>323</v>
       </c>
@@ -4872,7 +5082,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:7">
+    <row r="84" spans="1:7">
       <c r="A84" s="1" t="s">
         <v>323</v>
       </c>
@@ -4889,7 +5099,7 @@
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" hidden="1" spans="1:7">
+    <row r="85" spans="1:7">
       <c r="A85" s="1" t="s">
         <v>323</v>
       </c>
@@ -4912,7 +5122,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:7">
+    <row r="86" spans="1:7">
       <c r="A86" s="1" t="s">
         <v>330</v>
       </c>
@@ -4935,7 +5145,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:7">
+    <row r="87" spans="1:7">
       <c r="A87" s="1" t="s">
         <v>330</v>
       </c>
@@ -4952,7 +5162,7 @@
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" hidden="1" spans="1:7">
+    <row r="88" spans="1:7">
       <c r="A88" s="1" t="s">
         <v>330</v>
       </c>
@@ -4975,7 +5185,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:7">
+    <row r="89" spans="1:7">
       <c r="A89" s="1" t="s">
         <v>330</v>
       </c>
@@ -4998,7 +5208,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:7">
+    <row r="90" spans="1:7">
       <c r="A90" s="1" t="s">
         <v>330</v>
       </c>
@@ -5021,7 +5231,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:7">
+    <row r="91" spans="1:7">
       <c r="A91" s="1" t="s">
         <v>349</v>
       </c>
@@ -5044,7 +5254,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="1:7">
+    <row r="92" spans="1:7">
       <c r="A92" s="1" t="s">
         <v>349</v>
       </c>
@@ -5061,7 +5271,7 @@
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
     </row>
-    <row r="93" hidden="1" spans="1:7">
+    <row r="93" spans="1:7">
       <c r="A93" s="1" t="s">
         <v>349</v>
       </c>
@@ -5084,7 +5294,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="1:7">
+    <row r="94" spans="1:7">
       <c r="A94" s="1" t="s">
         <v>349</v>
       </c>
@@ -5107,7 +5317,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:7">
+    <row r="95" spans="1:7">
       <c r="A95" s="1" t="s">
         <v>349</v>
       </c>
@@ -5130,7 +5340,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:7">
+    <row r="96" spans="1:7">
       <c r="A96" s="1" t="s">
         <v>369</v>
       </c>
@@ -5153,7 +5363,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="1:7">
+    <row r="97" spans="1:7">
       <c r="A97" s="1" t="s">
         <v>369</v>
       </c>
@@ -5170,7 +5380,7 @@
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
     </row>
-    <row r="98" hidden="1" spans="1:7">
+    <row r="98" spans="1:7">
       <c r="A98" s="1" t="s">
         <v>369</v>
       </c>
@@ -5193,7 +5403,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:7">
+    <row r="99" spans="1:7">
       <c r="A99" s="1" t="s">
         <v>369</v>
       </c>
@@ -5216,7 +5426,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="100" hidden="1" spans="1:7">
+    <row r="100" spans="1:7">
       <c r="A100" s="1" t="s">
         <v>369</v>
       </c>
@@ -5239,7 +5449,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="1:7">
+    <row r="101" spans="1:7">
       <c r="A101" s="1" t="s">
         <v>388</v>
       </c>
@@ -5262,7 +5472,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:7">
+    <row r="102" spans="1:7">
       <c r="A102" s="1" t="s">
         <v>388</v>
       </c>
@@ -5279,7 +5489,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" hidden="1" spans="1:7">
+    <row r="103" spans="1:7">
       <c r="A103" s="1" t="s">
         <v>388</v>
       </c>
@@ -5302,7 +5512,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="104" hidden="1" spans="1:7">
+    <row r="104" spans="1:7">
       <c r="A104" s="1" t="s">
         <v>388</v>
       </c>
@@ -5325,7 +5535,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="1:7">
+    <row r="105" spans="1:7">
       <c r="A105" s="1" t="s">
         <v>388</v>
       </c>
@@ -5348,7 +5558,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="1:7">
+    <row r="106" spans="1:7">
       <c r="A106" s="1" t="s">
         <v>408</v>
       </c>
@@ -5371,7 +5581,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="1:7">
+    <row r="107" spans="1:7">
       <c r="A107" s="1" t="s">
         <v>408</v>
       </c>
@@ -5388,7 +5598,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" hidden="1" spans="1:7">
+    <row r="108" spans="1:7">
       <c r="A108" s="1" t="s">
         <v>408</v>
       </c>
@@ -5411,7 +5621,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:7">
+    <row r="109" spans="1:7">
       <c r="A109" s="1" t="s">
         <v>408</v>
       </c>
@@ -5434,7 +5644,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:7">
+    <row r="110" spans="1:7">
       <c r="A110" s="1" t="s">
         <v>408</v>
       </c>
@@ -5457,7 +5667,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="1:7">
+    <row r="111" spans="1:7">
       <c r="A111" s="1" t="s">
         <v>425</v>
       </c>
@@ -5480,7 +5690,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:7">
+    <row r="112" spans="1:7">
       <c r="A112" s="1" t="s">
         <v>425</v>
       </c>
@@ -5497,7 +5707,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" hidden="1" spans="1:7">
+    <row r="113" spans="1:7">
       <c r="A113" s="1" t="s">
         <v>425</v>
       </c>
@@ -5520,7 +5730,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="1:7">
+    <row r="114" spans="1:7">
       <c r="A114" s="1" t="s">
         <v>425</v>
       </c>
@@ -5543,7 +5753,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="115" hidden="1" spans="1:7">
+    <row r="115" spans="1:7">
       <c r="A115" s="1" t="s">
         <v>425</v>
       </c>
@@ -5566,7 +5776,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="116" hidden="1" spans="1:7">
+    <row r="116" spans="1:7">
       <c r="A116" s="1" t="s">
         <v>442</v>
       </c>
@@ -5587,7 +5797,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="117" hidden="1" spans="1:7">
+    <row r="117" spans="1:7">
       <c r="A117" s="1" t="s">
         <v>442</v>
       </c>
@@ -5604,7 +5814,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" hidden="1" spans="1:7">
+    <row r="118" spans="1:7">
       <c r="A118" s="1" t="s">
         <v>442</v>
       </c>
@@ -5627,7 +5837,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="1:7">
+    <row r="119" spans="1:7">
       <c r="A119" s="1" t="s">
         <v>442</v>
       </c>
@@ -5650,7 +5860,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="120" hidden="1" spans="1:7">
+    <row r="120" spans="1:7">
       <c r="A120" s="1" t="s">
         <v>453</v>
       </c>
@@ -5673,7 +5883,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="121" hidden="1" spans="1:7">
+    <row r="121" spans="1:7">
       <c r="A121" s="1" t="s">
         <v>453</v>
       </c>
@@ -5690,7 +5900,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" hidden="1" spans="1:7">
+    <row r="122" spans="1:7">
       <c r="A122" s="1" t="s">
         <v>453</v>
       </c>
@@ -5713,7 +5923,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="123" hidden="1" spans="1:7">
+    <row r="123" spans="1:7">
       <c r="A123" s="1" t="s">
         <v>453</v>
       </c>
@@ -5736,7 +5946,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="124" hidden="1" spans="1:7">
+    <row r="124" spans="1:7">
       <c r="A124" s="1" t="s">
         <v>453</v>
       </c>
@@ -5759,7 +5969,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="1:7">
+    <row r="125" spans="1:7">
       <c r="A125" s="1" t="s">
         <v>471</v>
       </c>
@@ -5782,7 +5992,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="1:7">
+    <row r="126" spans="1:7">
       <c r="A126" s="1" t="s">
         <v>471</v>
       </c>
@@ -5799,7 +6009,7 @@
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
     </row>
-    <row r="127" hidden="1" spans="1:7">
+    <row r="127" spans="1:7">
       <c r="A127" s="1" t="s">
         <v>471</v>
       </c>
@@ -5822,7 +6032,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="128" hidden="1" spans="1:7">
+    <row r="128" spans="1:7">
       <c r="A128" s="1" t="s">
         <v>471</v>
       </c>
@@ -5845,7 +6055,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="1:7">
+    <row r="129" spans="1:7">
       <c r="A129" s="1" t="s">
         <v>471</v>
       </c>
@@ -5868,7 +6078,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="130" hidden="1" spans="1:7">
+    <row r="130" spans="1:7">
       <c r="A130" s="1" t="s">
         <v>489</v>
       </c>
@@ -5891,7 +6101,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="131" hidden="1" spans="1:7">
+    <row r="131" spans="1:7">
       <c r="A131" s="1" t="s">
         <v>489</v>
       </c>
@@ -5908,7 +6118,7 @@
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
     </row>
-    <row r="132" hidden="1" spans="1:7">
+    <row r="132" spans="1:7">
       <c r="A132" s="1" t="s">
         <v>489</v>
       </c>
@@ -5931,7 +6141,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="133" hidden="1" spans="1:7">
+    <row r="133" spans="1:7">
       <c r="A133" s="1" t="s">
         <v>489</v>
       </c>
@@ -5954,7 +6164,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="134" hidden="1" spans="1:7">
+    <row r="134" spans="1:7">
       <c r="A134" s="1" t="s">
         <v>489</v>
       </c>
@@ -5977,7 +6187,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="135" hidden="1" spans="1:7">
+    <row r="135" spans="1:7">
       <c r="A135" s="1" t="s">
         <v>507</v>
       </c>
@@ -6000,7 +6210,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="136" hidden="1" spans="1:7">
+    <row r="136" spans="1:7">
       <c r="A136" s="1" t="s">
         <v>507</v>
       </c>
@@ -6017,7 +6227,7 @@
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
     </row>
-    <row r="137" hidden="1" spans="1:7">
+    <row r="137" spans="1:7">
       <c r="A137" s="1" t="s">
         <v>507</v>
       </c>
@@ -6040,7 +6250,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="138" hidden="1" spans="1:7">
+    <row r="138" spans="1:7">
       <c r="A138" s="1" t="s">
         <v>507</v>
       </c>
@@ -6063,7 +6273,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="139" hidden="1" spans="1:7">
+    <row r="139" spans="1:7">
       <c r="A139" s="1" t="s">
         <v>507</v>
       </c>
@@ -6086,7 +6296,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="140" hidden="1" spans="1:7">
+    <row r="140" spans="1:7">
       <c r="A140" s="1" t="s">
         <v>523</v>
       </c>
@@ -6109,7 +6319,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="141" hidden="1" spans="1:7">
+    <row r="141" spans="1:7">
       <c r="A141" s="1" t="s">
         <v>523</v>
       </c>
@@ -6126,7 +6336,7 @@
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>
     </row>
-    <row r="142" hidden="1" spans="1:7">
+    <row r="142" spans="1:7">
       <c r="A142" s="1" t="s">
         <v>523</v>
       </c>
@@ -6149,7 +6359,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="143" hidden="1" spans="1:7">
+    <row r="143" spans="1:7">
       <c r="A143" s="1" t="s">
         <v>523</v>
       </c>
@@ -6172,7 +6382,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="144" hidden="1" spans="1:7">
+    <row r="144" spans="1:7">
       <c r="A144" s="1" t="s">
         <v>523</v>
       </c>
@@ -6195,7 +6405,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="145" hidden="1" spans="1:7">
+    <row r="145" spans="1:7">
       <c r="A145" s="1" t="s">
         <v>539</v>
       </c>
@@ -6218,7 +6428,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="146" hidden="1" spans="1:7">
+    <row r="146" spans="1:7">
       <c r="A146" s="1" t="s">
         <v>539</v>
       </c>
@@ -6235,7 +6445,7 @@
       <c r="F146" s="1"/>
       <c r="G146" s="1"/>
     </row>
-    <row r="147" hidden="1" spans="1:7">
+    <row r="147" spans="1:7">
       <c r="A147" s="1" t="s">
         <v>539</v>
       </c>
@@ -6258,7 +6468,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="148" hidden="1" spans="1:7">
+    <row r="148" spans="1:7">
       <c r="A148" s="1" t="s">
         <v>539</v>
       </c>
@@ -6281,7 +6491,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="149" hidden="1" spans="1:7">
+    <row r="149" spans="1:7">
       <c r="A149" s="1" t="s">
         <v>539</v>
       </c>
@@ -6304,7 +6514,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="150" hidden="1" spans="1:7">
+    <row r="150" spans="1:7">
       <c r="A150" s="1" t="s">
         <v>556</v>
       </c>
@@ -6325,7 +6535,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="151" hidden="1" spans="1:7">
+    <row r="151" spans="1:7">
       <c r="A151" s="1" t="s">
         <v>556</v>
       </c>
@@ -6342,7 +6552,7 @@
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
     </row>
-    <row r="152" hidden="1" spans="1:7">
+    <row r="152" spans="1:7">
       <c r="A152" s="1" t="s">
         <v>556</v>
       </c>
@@ -6365,7 +6575,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="153" hidden="1" spans="1:7">
+    <row r="153" spans="1:7">
       <c r="A153" s="1" t="s">
         <v>561</v>
       </c>
@@ -6388,7 +6598,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="154" hidden="1" spans="1:7">
+    <row r="154" spans="1:7">
       <c r="A154" s="1" t="s">
         <v>561</v>
       </c>
@@ -6405,7 +6615,7 @@
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
     </row>
-    <row r="155" hidden="1" spans="1:7">
+    <row r="155" spans="1:7">
       <c r="A155" s="1" t="s">
         <v>561</v>
       </c>
@@ -6428,7 +6638,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="156" hidden="1" spans="1:7">
+    <row r="156" spans="1:7">
       <c r="A156" s="1" t="s">
         <v>561</v>
       </c>
@@ -6451,7 +6661,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="157" hidden="1" spans="1:7">
+    <row r="157" spans="1:7">
       <c r="A157" s="1" t="s">
         <v>561</v>
       </c>
@@ -6474,7 +6684,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="158" hidden="1" spans="1:7">
+    <row r="158" spans="1:7">
       <c r="A158" s="1" t="s">
         <v>578</v>
       </c>
@@ -6497,7 +6707,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="159" hidden="1" spans="1:7">
+    <row r="159" spans="1:7">
       <c r="A159" s="1" t="s">
         <v>578</v>
       </c>
@@ -6514,7 +6724,7 @@
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
     </row>
-    <row r="160" hidden="1" spans="1:7">
+    <row r="160" spans="1:7">
       <c r="A160" s="1" t="s">
         <v>578</v>
       </c>
@@ -6537,7 +6747,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="161" hidden="1" spans="1:7">
+    <row r="161" spans="1:7">
       <c r="A161" s="1" t="s">
         <v>578</v>
       </c>
@@ -6560,7 +6770,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="162" hidden="1" spans="1:7">
+    <row r="162" spans="1:7">
       <c r="A162" s="1" t="s">
         <v>578</v>
       </c>
@@ -6583,7 +6793,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="163" hidden="1" spans="1:7">
+    <row r="163" spans="1:7">
       <c r="A163" s="1" t="s">
         <v>595</v>
       </c>
@@ -6606,7 +6816,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="164" hidden="1" spans="1:7">
+    <row r="164" spans="1:7">
       <c r="A164" s="1" t="s">
         <v>595</v>
       </c>
@@ -6623,7 +6833,7 @@
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
     </row>
-    <row r="165" hidden="1" spans="1:7">
+    <row r="165" spans="1:7">
       <c r="A165" s="1" t="s">
         <v>595</v>
       </c>
@@ -6646,7 +6856,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="166" hidden="1" spans="1:7">
+    <row r="166" spans="1:7">
       <c r="A166" s="1" t="s">
         <v>595</v>
       </c>
@@ -6669,7 +6879,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="167" hidden="1" spans="1:7">
+    <row r="167" spans="1:7">
       <c r="A167" s="1" t="s">
         <v>595</v>
       </c>
@@ -7019,13 +7229,465 @@
         <v>667</v>
       </c>
     </row>
+    <row r="183" spans="1:7">
+      <c r="A183" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E183" s="1"/>
+      <c r="F183" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E184" s="1"/>
+      <c r="F184" s="1"/>
+      <c r="G184" s="1"/>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E189" s="1"/>
+      <c r="F189" s="1"/>
+      <c r="G189" s="1"/>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E194" s="1"/>
+      <c r="F194" s="1"/>
+      <c r="G194" s="1"/>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E199" s="1"/>
+      <c r="F199" s="1"/>
+      <c r="G199" s="1"/>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>737</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:V172" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="2026-08-07"/>
-      </filters>
-    </filterColumn>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:V192" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/uploads/zhuanhua_demo.xlsx
+++ b/data/uploads/zhuanhua_demo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="11740"/>
+    <workbookView windowWidth="26860" windowHeight="11740"/>
   </bookViews>
   <sheets>
     <sheet name="sheet" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="761">
   <si>
     <t>日期</t>
   </si>
@@ -2207,7 +2207,7 @@
     <t>0.01185835</t>
   </si>
   <si>
-    <t>其他</t>
+    <t>爆量未加微</t>
   </si>
   <si>
     <t>8.70</t>
@@ -2244,6 +2244,75 @@
   </si>
   <si>
     <t>0.03803291</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>483</t>
+  </si>
+  <si>
+    <t>3.63</t>
+  </si>
+  <si>
+    <t>0.00352331</t>
+  </si>
+  <si>
+    <t>0.01372783</t>
+  </si>
+  <si>
+    <t>1602</t>
+  </si>
+  <si>
+    <t>爆量再植课</t>
+  </si>
+  <si>
+    <t>959</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>8.88</t>
+  </si>
+  <si>
+    <t>0.00870876</t>
+  </si>
+  <si>
+    <t>0.03242933</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>1.66</t>
+  </si>
+  <si>
+    <t>0.00055502</t>
+  </si>
+  <si>
+    <t>0.00599700</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>5.78</t>
+  </si>
+  <si>
+    <t>0.00148116</t>
+  </si>
+  <si>
+    <t>0.02437310</t>
+  </si>
+  <si>
+    <t>8.50</t>
+  </si>
+  <si>
+    <t>0.01203753</t>
+  </si>
+  <si>
+    <t>0.02296521</t>
   </si>
 </sst>
 </file>
@@ -3258,7 +3327,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V203"/>
+  <dimension ref="A1:V209"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="7" width="16.8173076923077" customWidth="1"/>
@@ -7684,6 +7753,138 @@
       </c>
       <c r="G203" s="1" t="s">
         <v>737</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E205" s="1"/>
+      <c r="F205" s="1"/>
+      <c r="G205" s="1"/>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>760</v>
       </c>
     </row>
   </sheetData>

--- a/data/uploads/zhuanhua_demo.xlsx
+++ b/data/uploads/zhuanhua_demo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet!$A$1:$V$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet!$A$1:$V$228</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="454">
   <si>
     <t>日期</t>
   </si>
@@ -1320,19 +1320,92 @@
   </si>
   <si>
     <t>0.03450863</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>504</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>3.50</t>
+  </si>
+  <si>
+    <t>0.00358578</t>
+  </si>
+  <si>
+    <t>0.01424977</t>
+  </si>
+  <si>
+    <t>1857</t>
+  </si>
+  <si>
+    <t>1260</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>9.13</t>
+  </si>
+  <si>
+    <t>0.01184044</t>
+  </si>
+  <si>
+    <t>0.03296358</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>2.50</t>
+  </si>
+  <si>
+    <t>0.00091684</t>
+  </si>
+  <si>
+    <t>0.01130506</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>15.29</t>
+  </si>
+  <si>
+    <t>0.02247427</t>
+  </si>
+  <si>
+    <t>0.04220907</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>20260820</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="[$-409]yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1357,9 +1430,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1824,16 +1902,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1842,126 +1917,131 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2350,7 +2430,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:V218"/>
+  <dimension ref="A1:V233"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="7" width="16.8173076923077" customWidth="1"/>
@@ -6997,116 +7077,455 @@
       </c>
     </row>
     <row r="214" hidden="1" spans="1:7">
-      <c r="A214" s="6" t="s">
+      <c r="A214" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B214" s="6" t="s">
+      <c r="B214" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C214" s="6" t="s">
+      <c r="C214" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="D214" s="6" t="s">
+      <c r="D214" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E214" s="6"/>
-      <c r="F214" s="6"/>
-      <c r="G214" s="6"/>
+      <c r="E214" s="3"/>
+      <c r="F214" s="3"/>
+      <c r="G214" s="3"/>
     </row>
     <row r="215" hidden="1" spans="1:7">
-      <c r="A215" s="6" t="s">
+      <c r="A215" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B215" s="6" t="s">
+      <c r="B215" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C215" s="6" t="s">
+      <c r="C215" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="D215" s="6" t="s">
+      <c r="D215" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="E215" s="6" t="s">
+      <c r="E215" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="F215" s="6" t="s">
+      <c r="F215" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="G215" s="6" t="s">
+      <c r="G215" s="3" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="216" hidden="1" spans="1:7">
-      <c r="A216" s="6" t="s">
+      <c r="A216" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B216" s="6" t="s">
+      <c r="B216" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C216" s="6" t="s">
+      <c r="C216" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="D216" s="6" t="s">
+      <c r="D216" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="E216" s="6" t="s">
+      <c r="E216" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="F216" s="6" t="s">
+      <c r="F216" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="G216" s="6" t="s">
+      <c r="G216" s="3" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="217" spans="1:7">
-      <c r="A217" s="6" t="s">
+      <c r="A217" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="B217" s="6" t="s">
+      <c r="B217" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C217" s="6" t="s">
+      <c r="C217" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="D217" s="6" t="s">
+      <c r="D217" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E217" s="6"/>
-      <c r="F217" s="6"/>
-      <c r="G217" s="6"/>
+      <c r="E217" s="3"/>
+      <c r="F217" s="3"/>
+      <c r="G217" s="3"/>
     </row>
     <row r="218" spans="1:7">
-      <c r="A218" s="6" t="s">
+      <c r="A218" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="B218" s="6" t="s">
+      <c r="B218" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C218" s="6" t="s">
+      <c r="C218" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="D218" s="6" t="s">
+      <c r="D218" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="E218" s="6" t="s">
+      <c r="E218" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="F218" s="6" t="s">
+      <c r="F218" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="G218" s="6" t="s">
+      <c r="G218" s="3" t="s">
         <v>429</v>
       </c>
     </row>
+    <row r="219" spans="1:7">
+      <c r="A219" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E220" s="3"/>
+      <c r="F220" s="3"/>
+      <c r="G220" s="3"/>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B224" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C224" s="7">
+        <v>481</v>
+      </c>
+      <c r="D224" s="7">
+        <v>141</v>
+      </c>
+      <c r="E224" s="7">
+        <v>3.4113475177305</v>
+      </c>
+      <c r="F224" s="7">
+        <v>0.00331749305119699</v>
+      </c>
+      <c r="G224" s="7">
+        <v>0.0149309327952817</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B225" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C225" s="7">
+        <v>817</v>
+      </c>
+      <c r="D225" s="7">
+        <v>0</v>
+      </c>
+      <c r="E225" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="F225" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="G225" s="7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B226" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="C226" s="7">
+        <v>874</v>
+      </c>
+      <c r="D226" s="7">
+        <v>131</v>
+      </c>
+      <c r="E226" s="7">
+        <v>6.67175572519084</v>
+      </c>
+      <c r="F226" s="7">
+        <v>0.0060008513793719</v>
+      </c>
+      <c r="G226" s="7">
+        <v>0.0234876783746742</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B227" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C227" s="7">
+        <v>98</v>
+      </c>
+      <c r="D227" s="7">
+        <v>49</v>
+      </c>
+      <c r="E227" s="7">
+        <v>2</v>
+      </c>
+      <c r="F227" s="7">
+        <v>0.000834106442195572</v>
+      </c>
+      <c r="G227" s="7">
+        <v>0.00951548694047966</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B228" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C228" s="7">
+        <v>97</v>
+      </c>
+      <c r="D228" s="7">
+        <v>8</v>
+      </c>
+      <c r="E228" s="7">
+        <v>12.125</v>
+      </c>
+      <c r="F228" s="7">
+        <v>0.0193844924060751</v>
+      </c>
+      <c r="G228" s="7">
+        <v>0.0355571847507331</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B229" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C229" s="8">
+        <v>592</v>
+      </c>
+      <c r="D229" s="8">
+        <v>144</v>
+      </c>
+      <c r="E229" s="8">
+        <v>4.11111111111111</v>
+      </c>
+      <c r="F229" s="8">
+        <v>0.00336377014994915</v>
+      </c>
+      <c r="G229" s="8">
+        <v>0.0185970533722866</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B230" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C230" s="8">
+        <v>1058</v>
+      </c>
+      <c r="D230" s="8">
+        <v>0</v>
+      </c>
+      <c r="E230" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="F230" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="G230" s="8" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B231" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C231" s="8">
+        <v>126</v>
+      </c>
+      <c r="D231" s="8">
+        <v>50</v>
+      </c>
+      <c r="E231" s="8">
+        <v>2.52</v>
+      </c>
+      <c r="F231" s="8">
+        <v>0.000965916931143922</v>
+      </c>
+      <c r="G231" s="8">
+        <v>0.0119239140721113</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B232" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C232" s="8">
+        <v>84</v>
+      </c>
+      <c r="D232" s="8">
+        <v>8</v>
+      </c>
+      <c r="E232" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="F232" s="8">
+        <v>0.0158371040723982</v>
+      </c>
+      <c r="G232" s="8">
+        <v>0.0313082370480805</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B233" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C233" s="8">
+        <v>903</v>
+      </c>
+      <c r="D233" s="8">
+        <v>136</v>
+      </c>
+      <c r="E233" s="8">
+        <v>6.63970588235294</v>
+      </c>
+      <c r="F233" s="8">
+        <v>0.00657506717053671</v>
+      </c>
+      <c r="G233" s="8">
+        <v>0.0230263157894737</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:V216" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:V228" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="1">
-      <filters>
-        <filter val="大神"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="大神"/>
+      </customFilters>
     </filterColumn>
-    <sortState ref="A2:V216">
+    <sortState ref="A1:V228">
       <sortCondition ref="A1" descending="1"/>
     </sortState>
     <extLst/>

--- a/data/uploads/zhuanhua_demo.xlsx
+++ b/data/uploads/zhuanhua_demo.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="458">
   <si>
     <t>日期</t>
   </si>
@@ -1392,6 +1392,18 @@
   </si>
   <si>
     <t>20260820</t>
+  </si>
+  <si>
+    <t>20260821</t>
+  </si>
+  <si>
+    <t>20260822</t>
+  </si>
+  <si>
+    <t>20260823</t>
+  </si>
+  <si>
+    <t>20260824</t>
   </si>
 </sst>
 </file>
@@ -2430,7 +2442,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:V233"/>
+  <dimension ref="A1:V252"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="7" width="16.8173076923077" customWidth="1"/>
@@ -7516,6 +7528,443 @@
       </c>
       <c r="G233" s="8">
         <v>0.0230263157894737</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="B234" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C234" s="8">
+        <v>130</v>
+      </c>
+      <c r="D234" s="8">
+        <v>51</v>
+      </c>
+      <c r="E234" s="8">
+        <v>2.54901960784314</v>
+      </c>
+      <c r="F234" s="8">
+        <v>0.0115576102418208</v>
+      </c>
+      <c r="G234" s="8">
+        <v>0.014207650273224</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="B235" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C235" s="8">
+        <v>793</v>
+      </c>
+      <c r="D235" s="8">
+        <v>130</v>
+      </c>
+      <c r="E235" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="F235" s="8">
+        <v>0.0212549250851001</v>
+      </c>
+      <c r="G235" s="8">
+        <v>0.0350002206823498</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="B236" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C236" s="8">
+        <v>1326</v>
+      </c>
+      <c r="D236" s="8">
+        <v>0</v>
+      </c>
+      <c r="E236" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="F236" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="G236" s="8" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="B237" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C237" s="8">
+        <v>588</v>
+      </c>
+      <c r="D237" s="8">
+        <v>142</v>
+      </c>
+      <c r="E237" s="8">
+        <v>4.14084507042254</v>
+      </c>
+      <c r="F237" s="8">
+        <v>0.0206634804610627</v>
+      </c>
+      <c r="G237" s="8">
+        <v>0.029215939580642</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="B238" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C238" s="8">
+        <v>71</v>
+      </c>
+      <c r="D238" s="8">
+        <v>8</v>
+      </c>
+      <c r="E238" s="8">
+        <v>8.875</v>
+      </c>
+      <c r="F238" s="8">
+        <v>0.025884068538097</v>
+      </c>
+      <c r="G238" s="8">
+        <v>0.0309098824553766</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="B239" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C239" s="8">
+        <v>523</v>
+      </c>
+      <c r="D239" s="8">
+        <v>143</v>
+      </c>
+      <c r="E239" s="8">
+        <v>3.65734265734266</v>
+      </c>
+      <c r="F239" s="8">
+        <v>0.00319555188953044</v>
+      </c>
+      <c r="G239" s="8">
+        <v>0.0156929816665166</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="B240" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C240" s="8">
+        <v>1152</v>
+      </c>
+      <c r="D240" s="8">
+        <v>0</v>
+      </c>
+      <c r="E240" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="F240" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="G240" s="8" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="B241" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C241" s="8">
+        <v>99</v>
+      </c>
+      <c r="D241" s="8">
+        <v>13</v>
+      </c>
+      <c r="E241" s="8">
+        <v>7.61538461538461</v>
+      </c>
+      <c r="F241" s="8">
+        <v>0.0114929185047597</v>
+      </c>
+      <c r="G241" s="8">
+        <v>0.0221724524076148</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="B242" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C242" s="8">
+        <v>90</v>
+      </c>
+      <c r="D242" s="8">
+        <v>52</v>
+      </c>
+      <c r="E242" s="8">
+        <v>1.73076923076923</v>
+      </c>
+      <c r="F242" s="8">
+        <v>0.00078438891745614</v>
+      </c>
+      <c r="G242" s="8">
+        <v>0.00781114389862871</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="B243" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C243" s="8">
+        <v>776</v>
+      </c>
+      <c r="D243" s="8">
+        <v>130</v>
+      </c>
+      <c r="E243" s="8">
+        <v>5.96923076923077</v>
+      </c>
+      <c r="F243" s="8">
+        <v>0.00732255081435069</v>
+      </c>
+      <c r="G243" s="8">
+        <v>0.0213374395072591</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="B244" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C244" s="8">
+        <v>420</v>
+      </c>
+      <c r="D244" s="8">
+        <v>140</v>
+      </c>
+      <c r="E244" s="8">
+        <v>3</v>
+      </c>
+      <c r="F244" s="8">
+        <v>0.00222789214880198</v>
+      </c>
+      <c r="G244" s="8">
+        <v>0.012821686967671</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="B245" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C245" s="8">
+        <v>835</v>
+      </c>
+      <c r="D245" s="8">
+        <v>0</v>
+      </c>
+      <c r="E245" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="F245" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="G245" s="8" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="B246" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C246" s="8">
+        <v>743</v>
+      </c>
+      <c r="D246" s="8">
+        <v>131</v>
+      </c>
+      <c r="E246" s="8">
+        <v>5.67175572519084</v>
+      </c>
+      <c r="F246" s="8">
+        <v>0.0036552009130623</v>
+      </c>
+      <c r="G246" s="8">
+        <v>0.0215549753408761</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="B247" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C247" s="8">
+        <v>88</v>
+      </c>
+      <c r="D247" s="8">
+        <v>49</v>
+      </c>
+      <c r="E247" s="8">
+        <v>1.79591836734694</v>
+      </c>
+      <c r="F247" s="8">
+        <v>0.000554257389573663</v>
+      </c>
+      <c r="G247" s="8">
+        <v>0.00785013380909902</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="B248" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C248" s="8">
+        <v>72</v>
+      </c>
+      <c r="D248" s="8">
+        <v>11</v>
+      </c>
+      <c r="E248" s="8">
+        <v>6.54545454545455</v>
+      </c>
+      <c r="F248" s="8">
+        <v>0.0105494505494505</v>
+      </c>
+      <c r="G248" s="8">
+        <v>0.0215439856373429</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="B249" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C249" s="8">
+        <v>0</v>
+      </c>
+      <c r="D249" s="8">
+        <v>0</v>
+      </c>
+      <c r="E249" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="F249" s="8">
+        <v>0</v>
+      </c>
+      <c r="G249" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="B250" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C250" s="8">
+        <v>712</v>
+      </c>
+      <c r="D250" s="8">
+        <v>0</v>
+      </c>
+      <c r="E250" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="F250" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="G250" s="8" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="B251" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C251" s="8">
+        <v>89</v>
+      </c>
+      <c r="D251" s="8">
+        <v>33</v>
+      </c>
+      <c r="E251" s="8">
+        <v>2.6969696969697</v>
+      </c>
+      <c r="F251" s="8">
+        <v>0.00111708002811527</v>
+      </c>
+      <c r="G251" s="8">
+        <v>0.0120400432900433</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="B252" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C252" s="8">
+        <v>231</v>
+      </c>
+      <c r="D252" s="8">
+        <v>24</v>
+      </c>
+      <c r="E252" s="8">
+        <v>9.625</v>
+      </c>
+      <c r="F252" s="8">
+        <v>0.00719895287958115</v>
+      </c>
+      <c r="G252" s="8">
+        <v>0.0332326283987915</v>
       </c>
     </row>
   </sheetData>
